--- a/Дневники/Мазур Иван.xlsx
+++ b/Дневники/Мазур Иван.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\УП.02.01 Ролевая игра Проектная группа\Отчет\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\УП.02.01 Ролевая игра Проектная группа\Отчет Дневники\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D62C67-B4DC-45BE-8B8E-E5F9DA96B88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD56A09-6BA0-4052-A25B-70573A8F3382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Дата1" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Задача</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Время выполнения</t>
   </si>
   <si>
-    <t>Филатов Н.А.</t>
-  </si>
-  <si>
     <t>Дизайнер</t>
   </si>
   <si>
@@ -67,6 +64,24 @@
   </si>
   <si>
     <t>Тестировщик Клиентской части</t>
+  </si>
+  <si>
+    <t>День 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>День 2</t>
+  </si>
+  <si>
+    <t>День 3</t>
+  </si>
+  <si>
+    <t>День 5</t>
+  </si>
+  <si>
+    <t>Мазур И.Д.</t>
   </si>
 </sst>
 </file>
@@ -184,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -211,6 +226,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -493,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942723FC-F17B-4EAF-B780-F95BEB36B17D}">
-  <dimension ref="B2:D51"/>
+  <dimension ref="A2:D51"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="2"/>
@@ -503,14 +521,14 @@
     <col min="5" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -521,103 +539,114 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="4">
         <v>0.36458333333333331</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="7"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>0.34375</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4">
         <v>0.47916666666666669</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>0.47916666666666669</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="4">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="7"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>0.34375</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4">
         <v>0.4861111111111111</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>0.4861111111111111</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="C12" s="8"/>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>0.33333333333333331</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -799,11 +828,12 @@
     </row>
   </sheetData>
   <autoFilter ref="B3:D3" xr:uid="{942723FC-F17B-4EAF-B780-F95BEB36B17D}"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B4:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
